--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dp-practitioner</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dp-practitioner</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T12:29:31+00:00</t>
+    <t>2023-06-02T14:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -354,7 +354,7 @@
     <t>as-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
 </t>
   </si>
   <si>
@@ -597,7 +597,7 @@
     <t>as-ext-practitioner-nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-nationality}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-nationality}
 </t>
   </si>
   <si>
@@ -613,7 +613,7 @@
     <t>as-ext-frpractitioner-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization}
 </t>
   </si>
   <si>
@@ -629,7 +629,7 @@
     <t>as-ext-practitioner-birth-place</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-birth-place}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-birth-place}
 </t>
   </si>
   <si>
@@ -645,7 +645,7 @@
     <t>as-ext-practitioner-deceased-date-time</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-deceased-date-time}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-deceased-date-time}
 </t>
   </si>
   <si>
@@ -1208,7 +1208,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
 </t>
   </si>
   <si>
@@ -1362,7 +1362,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended}
 </t>
   </si>
   <si>
@@ -2036,7 +2036,7 @@
     <t>Practitioner.communication</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
 </t>
   </si>
   <si>
@@ -2374,7 +2374,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="108.4921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="109.44921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T14:39:58+00:00</t>
+    <t>2023-06-02T15:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
